--- a/jpcore-r4/develop/StructureDefinition-jp-obsrevation-electrocardiogram-numberoflead.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-obsrevation-electrocardiogram-numberoflead.xlsx
@@ -87,7 +87,7 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>心電図検査で仕様する誘導の数を記録するために用いられる。</t>
+    <t>心電図検査で使用した誘導の数を記録するために用いられる。</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -135,7 +135,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Observation.lead</t>
+    <t>element:Observation</t>
   </si>
   <si>
     <t>ID</t>
@@ -265,7 +265,7 @@
     <t>誘導の数</t>
   </si>
   <si>
-    <t>心電図検査で試用した誘導の数を記録するための拡張</t>
+    <t>心電図検査で使用した誘導の数を記録するための拡張</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -347,7 +347,7 @@
 </t>
   </si>
   <si>
-    <t>心電図検査を実施したときに試用した誘導の数</t>
+    <t>心電図検査で使用した誘導の数</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
